--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3797,9 +3797,14 @@
       <c r="E100" s="4" t="n">
         <v>46278.10625</v>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1623146819400971</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3830,9 +3830,14 @@
       <c r="E101" s="4" t="n">
         <v>46278.23125</v>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1068214979331557</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3863,9 +3863,14 @@
       <c r="E102" s="4" t="n">
         <v>46278.73125</v>
       </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2008234689881124</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3896,9 +3896,14 @@
       <c r="E103" s="4" t="n">
         <v>46278.85625</v>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1595654005389303</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3929,9 +3929,14 @@
       <c r="E104" s="4" t="n">
         <v>46278.98125</v>
       </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1670325584657174</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3962,9 +3962,14 @@
       <c r="E105" s="4" t="n">
         <v>46279.10625</v>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2236487510465362</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3995,9 +3995,14 @@
       <c r="E106" s="4" t="n">
         <v>46279.23125</v>
       </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1753061162478685</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4028,9 +4028,14 @@
       <c r="E107" s="4" t="n">
         <v>46279.73125</v>
       </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1414700430586777</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4061,9 +4061,14 @@
       <c r="E108" s="4" t="n">
         <v>46279.85625</v>
       </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1058260950386129</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4094,9 +4094,14 @@
       <c r="E109" s="4" t="n">
         <v>46279.98125</v>
       </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1607416207631890</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4127,9 +4127,14 @@
       <c r="E110" s="4" t="n">
         <v>46280.10625</v>
       </c>
-      <c r="F110" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1411700467597843</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4160,9 +4160,14 @@
       <c r="E111" s="4" t="n">
         <v>46280.23125</v>
       </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>28475125722128514</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4193,9 +4193,14 @@
       <c r="E112" s="4" t="n">
         <v>46280.73125</v>
       </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1123670357273778</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4226,9 +4226,14 @@
       <c r="E113" s="4" t="n">
         <v>46280.85625</v>
       </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1747536323212649</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4259,9 +4259,14 @@
       <c r="E114" s="4" t="n">
         <v>46280.98125</v>
       </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1136064452281687</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4292,9 +4292,14 @@
       <c r="E115" s="4" t="n">
         <v>46281.10625</v>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1636217328087472</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4325,9 +4325,14 @@
       <c r="E116" s="4" t="n">
         <v>46281.23125</v>
       </c>
-      <c r="F116" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>3047999158877267</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4358,9 +4358,14 @@
       <c r="E117" s="4" t="n">
         <v>46281.73125</v>
       </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>977506812040256</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4391,9 +4391,14 @@
       <c r="E118" s="4" t="n">
         <v>46281.85625</v>
       </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1064185729922870</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4424,9 +4424,14 @@
       <c r="E119" s="4" t="n">
         <v>46281.98125</v>
       </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1786087296143901</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4457,9 +4457,14 @@
       <c r="E120" s="4" t="n">
         <v>46282.10625</v>
       </c>
-      <c r="F120" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1665148798613079</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4490,9 +4490,14 @@
       <c r="E121" s="4" t="n">
         <v>46282.23125</v>
       </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1034280482945872</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4523,9 +4523,14 @@
       <c r="E122" s="4" t="n">
         <v>46282.73125</v>
       </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1397070168554216</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4556,9 +4556,14 @@
       <c r="E123" s="4" t="n">
         <v>46282.85625</v>
       </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>1752569649323341</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4589,9 +4589,14 @@
       <c r="E124" s="4" t="n">
         <v>46282.98125</v>
       </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>965631102716355</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4622,9 +4622,14 @@
       <c r="E125" s="4" t="n">
         <v>46283.10625</v>
       </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1594824725441257</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4655,9 +4655,14 @@
       <c r="E126" s="4" t="n">
         <v>46283.23125</v>
       </c>
-      <c r="F126" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>1820422272658038</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4688,9 +4688,14 @@
       <c r="E127" s="4" t="n">
         <v>46283.73125</v>
       </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2297724924312848</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4721,9 +4721,14 @@
       <c r="E128" s="4" t="n">
         <v>46283.85625</v>
       </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1092822649967614</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4754,9 +4754,14 @@
       <c r="E129" s="4" t="n">
         <v>46283.98125</v>
       </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>1702286787532685</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4787,9 +4787,14 @@
       <c r="E130" s="4" t="n">
         <v>46284.10625</v>
       </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>1621510829358300</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4820,9 +4820,14 @@
       <c r="E131" s="4" t="n">
         <v>46284.23125</v>
       </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>1133301949369670</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4853,9 +4853,14 @@
       <c r="E132" s="4" t="n">
         <v>46284.73125</v>
       </c>
-      <c r="F132" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>947006451798898</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4886,9 +4886,14 @@
       <c r="E133" s="4" t="n">
         <v>46284.85625</v>
       </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>1332383618786693</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4919,9 +4919,14 @@
       <c r="E134" s="4" t="n">
         <v>46284.98125</v>
       </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>1077422731880837</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4952,9 +4952,14 @@
       <c r="E135" s="4" t="n">
         <v>46285.10625</v>
       </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>1311356342063999</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4985,9 +4985,14 @@
       <c r="E136" s="4" t="n">
         <v>46285.23125</v>
       </c>
-      <c r="F136" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>1517011233777497</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5018,9 +5018,14 @@
       <c r="E137" s="4" t="n">
         <v>46285.73125</v>
       </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>1613344180160362</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5051,9 +5051,14 @@
       <c r="E138" s="4" t="n">
         <v>46285.85625</v>
       </c>
-      <c r="F138" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>1072033648937680</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5084,9 +5084,14 @@
       <c r="E139" s="4" t="n">
         <v>46285.98125</v>
       </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2310394003112922</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5117,9 +5117,14 @@
       <c r="E140" s="4" t="n">
         <v>46286.10625</v>
       </c>
-      <c r="F140" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2553805801722231</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5150,9 +5150,14 @@
       <c r="E141" s="4" t="n">
         <v>46286.23125</v>
       </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>28361393113524314</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5183,9 +5183,14 @@
       <c r="E142" s="4" t="n">
         <v>46286.73125</v>
       </c>
-      <c r="F142" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>1749293619687966</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5216,9 +5216,14 @@
       <c r="E143" s="4" t="n">
         <v>46286.85625</v>
       </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>28005976395770185</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5249,9 +5249,14 @@
       <c r="E144" s="4" t="n">
         <v>46286.98125</v>
       </c>
-      <c r="F144" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2202731033791260</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5282,9 +5282,14 @@
       <c r="E145" s="4" t="n">
         <v>46287.10625</v>
       </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>1619557932914324</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5315,9 +5315,14 @@
       <c r="E146" s="4" t="n">
         <v>46287.23125</v>
       </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F146" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1099695949313128</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5348,9 +5348,14 @@
       <c r="E147" s="4" t="n">
         <v>46287.73125</v>
       </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2578859412563829</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5381,9 +5381,14 @@
       <c r="E148" s="4" t="n">
         <v>46287.85625</v>
       </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>1941424943484567</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5414,9 +5414,14 @@
       <c r="E149" s="4" t="n">
         <v>46287.98125</v>
       </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1079941764400917</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5447,9 +5447,14 @@
       <c r="E150" s="4" t="n">
         <v>46288.10625</v>
       </c>
-      <c r="F150" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>1998792940837859</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5480,9 +5480,14 @@
       <c r="E151" s="4" t="n">
         <v>46288.23125</v>
       </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2334050534045681</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5513,9 +5513,14 @@
       <c r="E152" s="4" t="n">
         <v>46288.73125</v>
       </c>
-      <c r="F152" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F152" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>1735970658056075</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5546,9 +5546,14 @@
       <c r="E153" s="4" t="n">
         <v>46288.85625</v>
       </c>
-      <c r="F153" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F153" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>1566930907916220</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5579,9 +5579,14 @@
       <c r="E154" s="4" t="n">
         <v>46288.98125</v>
       </c>
-      <c r="F154" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F154" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>1545594337368342</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5612,9 +5612,14 @@
       <c r="E155" s="4" t="n">
         <v>46289.10625</v>
       </c>
-      <c r="F155" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F155" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>1658842719283176</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5645,9 +5645,14 @@
       <c r="E156" s="4" t="n">
         <v>46289.23125</v>
       </c>
-      <c r="F156" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F156" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>1306762721438172</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5678,9 +5678,14 @@
       <c r="E157" s="4" t="n">
         <v>46289.73125</v>
       </c>
-      <c r="F157" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F157" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>1783199489383870</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5711,9 +5711,14 @@
       <c r="E158" s="4" t="n">
         <v>46289.85625</v>
       </c>
-      <c r="F158" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F158" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>1646429546851715</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5744,9 +5744,14 @@
       <c r="E159" s="4" t="n">
         <v>46289.98125</v>
       </c>
-      <c r="F159" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F159" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>1123617613516879</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5777,9 +5777,14 @@
       <c r="E160" s="4" t="n">
         <v>46290.10625</v>
       </c>
-      <c r="F160" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F160" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>1104346548830035</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5810,9 +5810,14 @@
       <c r="E161" s="4" t="n">
         <v>46290.23125</v>
       </c>
-      <c r="F161" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F161" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>1589343926328829</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5843,9 +5843,14 @@
       <c r="E162" s="4" t="n">
         <v>46290.73125</v>
       </c>
-      <c r="F162" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>4663820127198605</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5876,9 +5876,14 @@
       <c r="E163" s="4" t="n">
         <v>46290.85625</v>
       </c>
-      <c r="F163" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F163" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>1807119186997751</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5909,9 +5909,14 @@
       <c r="E164" s="4" t="n">
         <v>46290.98125</v>
       </c>
-      <c r="F164" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F164" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>1738594380704563</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5942,9 +5942,14 @@
       <c r="E165" s="4" t="n">
         <v>46291.10625</v>
       </c>
-      <c r="F165" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F165" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>1358499006267391</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5975,9 +5975,14 @@
       <c r="E166" s="4" t="n">
         <v>46291.23125</v>
       </c>
-      <c r="F166" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F166" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>1708359050229004</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6008,9 +6008,14 @@
       <c r="E167" s="4" t="n">
         <v>46291.73125</v>
       </c>
-      <c r="F167" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F167" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>1578165987656197</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6041,9 +6041,14 @@
       <c r="E168" s="4" t="n">
         <v>46291.85625</v>
       </c>
-      <c r="F168" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F168" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2123885971540289</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6074,9 +6074,14 @@
       <c r="E169" s="4" t="n">
         <v>46291.98125</v>
       </c>
-      <c r="F169" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F169" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>1439293874852492</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6107,9 +6107,14 @@
       <c r="E170" s="4" t="n">
         <v>46292.10625</v>
       </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F170" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2290005201776910</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6140,9 +6140,14 @@
       <c r="E171" s="4" t="n">
         <v>46292.23125</v>
       </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>1736547010791874</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6173,9 +6173,14 @@
       <c r="E172" s="4" t="n">
         <v>46292.73125</v>
       </c>
-      <c r="F172" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F172" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>1417519229711579</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -6206,9 +6206,14 @@
       <c r="E173" s="4" t="n">
         <v>46292.85625</v>
       </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F173" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>4767432210165322</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -638,9 +638,14 @@
       <c r="E2" s="4" t="n">
         <v>46292.98125</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1978226436209020</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -704,9 +704,14 @@
       <c r="E4" s="4" t="n">
         <v>46293.10625</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1683321470251037</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -737,9 +737,14 @@
       <c r="E5" s="4" t="n">
         <v>46293.23125</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1148929140995582</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -770,9 +770,14 @@
       <c r="E6" s="4" t="n">
         <v>46293.73125</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1397254932608783</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -869,9 +869,14 @@
       <c r="E9" s="4" t="n">
         <v>46293.85625</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1837631293943056</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -902,9 +902,14 @@
       <c r="E10" s="4" t="n">
         <v>46293.98125</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1637733967748577</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -968,9 +968,14 @@
       <c r="E12" s="4" t="n">
         <v>46294.10625</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1709791920105510</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1001,9 +1001,14 @@
       <c r="E13" s="4" t="n">
         <v>46294.23125</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1820866842670406</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1034,9 +1034,14 @@
       <c r="E14" s="4" t="n">
         <v>46294.73125</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1626274365876271</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1067,9 +1067,14 @@
       <c r="E15" s="4" t="n">
         <v>46294.85625</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2605082133274372</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1100,9 +1100,14 @@
       <c r="E16" s="4" t="n">
         <v>46294.98125</v>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>27821505727527610</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1133,9 +1133,14 @@
       <c r="E17" s="4" t="n">
         <v>46295.10625</v>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1428765802549063</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1166,9 +1166,14 @@
       <c r="E18" s="4" t="n">
         <v>46295.23125</v>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1125400366811281</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1298,9 +1298,14 @@
       <c r="E22" s="4" t="n">
         <v>46295.73125</v>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2173630609915064</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1331,9 +1331,14 @@
       <c r="E23" s="4" t="n">
         <v>46295.85625</v>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1129871473295906</t>
         </is>
       </c>
     </row>
